--- a/src/assets/distress/רשימת עובדות בגנים.xlsx
+++ b/src/assets/distress/רשימת עובדות בגנים.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/dba97155a5237de2/claude/status/src/assets/distress/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guy\OneDrive\claude\status\src\assets\distress\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="41" documentId="8_{E5DF85AC-C873-44AE-8EA0-71B025B2A856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8497432-3DF4-4FA2-BFEC-8B3373AEC4CB}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5552F21-F8E1-45FE-BC59-523F221BE5B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{97E04764-DA33-4F52-9FCC-5A19227C4015}"/>
+    <workbookView xWindow="-9450" yWindow="1200" windowWidth="7635" windowHeight="10560" xr2:uid="{97E04764-DA33-4F52-9FCC-5A19227C4015}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="47">
   <si>
     <t>משנה</t>
   </si>
@@ -50,9 +50,6 @@
     <t>גנון חצב</t>
   </si>
   <si>
-    <t>הגיל הרך-כללי</t>
-  </si>
-  <si>
     <t>פעוטון אורנים</t>
   </si>
   <si>
@@ -126,18 +123,6 @@
   </si>
   <si>
     <t>אלה לפידות</t>
-  </si>
-  <si>
-    <t>רותי צור טובי</t>
-  </si>
-  <si>
-    <t>צפורה חג ברגמן</t>
-  </si>
-  <si>
-    <t>פנינה מרקר</t>
-  </si>
-  <si>
-    <t>קרן בן אברהם קו</t>
   </si>
   <si>
     <t>ליאורה לוי</t>
@@ -584,13 +569,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC6318CB-6AE0-41E8-B68F-5E7820C899EF}">
-  <dimension ref="A1:I52"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:I48"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="17.399999999999999" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:9" ht="18" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>0</v>
@@ -603,14 +588,14 @@
       <c r="H1" s="3"/>
       <c r="I1" s="4"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="5"/>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="7"/>
       <c r="D2" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
@@ -618,14 +603,14 @@
       <c r="H2" s="6"/>
       <c r="I2" s="7"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="5"/>
       <c r="B3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="7"/>
       <c r="D3" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
@@ -633,14 +618,14 @@
       <c r="H3" s="6"/>
       <c r="I3" s="7"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="5"/>
       <c r="B4" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="7"/>
       <c r="D4" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="6"/>
       <c r="F4" s="6"/>
@@ -648,14 +633,14 @@
       <c r="H4" s="6"/>
       <c r="I4" s="7"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="5"/>
       <c r="B5" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -663,14 +648,14 @@
       <c r="H5" s="6"/>
       <c r="I5" s="7"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="5"/>
       <c r="B6" t="s">
         <v>1</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" s="6"/>
@@ -678,14 +663,14 @@
       <c r="H6" s="6"/>
       <c r="I6" s="7"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="5"/>
       <c r="B7" t="s">
         <v>1</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="6"/>
       <c r="F7" s="6"/>
@@ -693,14 +678,14 @@
       <c r="H7" s="6"/>
       <c r="I7" s="7"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="5"/>
       <c r="B8" t="s">
         <v>1</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
@@ -708,7 +693,7 @@
       <c r="H8" s="6"/>
       <c r="I8" s="7"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="5"/>
       <c r="C9" s="7"/>
       <c r="D9" s="6"/>
@@ -718,14 +703,14 @@
       <c r="H9" s="6"/>
       <c r="I9" s="7"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="5"/>
       <c r="B10" t="s">
         <v>2</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E10" s="6"/>
       <c r="F10" s="6"/>
@@ -733,14 +718,14 @@
       <c r="H10" s="6"/>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="5"/>
       <c r="B11" t="s">
         <v>2</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E11" s="6"/>
       <c r="F11" s="6"/>
@@ -748,14 +733,14 @@
       <c r="H11" s="6"/>
       <c r="I11" s="7"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="5"/>
       <c r="B12" t="s">
         <v>2</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
@@ -763,14 +748,14 @@
       <c r="H12" s="6"/>
       <c r="I12" s="7"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="5"/>
       <c r="B13" t="s">
         <v>2</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E13" s="6"/>
       <c r="F13" s="6"/>
@@ -778,14 +763,14 @@
       <c r="H13" s="6"/>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="5"/>
       <c r="B14" t="s">
         <v>2</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" s="6"/>
       <c r="F14" s="6"/>
@@ -793,14 +778,14 @@
       <c r="H14" s="6"/>
       <c r="I14" s="7"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="5"/>
       <c r="B15" t="s">
         <v>2</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" s="6"/>
       <c r="F15" s="6"/>
@@ -808,14 +793,14 @@
       <c r="H15" s="6"/>
       <c r="I15" s="7"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="5"/>
       <c r="B16" t="s">
         <v>2</v>
       </c>
       <c r="C16" s="7"/>
       <c r="D16" s="6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E16" s="6"/>
       <c r="F16" s="6"/>
@@ -823,14 +808,14 @@
       <c r="H16" s="6"/>
       <c r="I16" s="7"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="5"/>
       <c r="B17" t="s">
         <v>2</v>
       </c>
       <c r="C17" s="7"/>
       <c r="D17" s="6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E17" s="6"/>
       <c r="F17" s="6"/>
@@ -838,7 +823,7 @@
       <c r="H17" s="6"/>
       <c r="I17" s="7"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="5"/>
       <c r="C18" s="7"/>
       <c r="D18" s="6"/>
@@ -848,14 +833,14 @@
       <c r="H18" s="6"/>
       <c r="I18" s="7"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="5"/>
       <c r="B19" t="s">
         <v>3</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E19" s="6"/>
       <c r="F19" s="6"/>
@@ -863,14 +848,14 @@
       <c r="H19" s="6"/>
       <c r="I19" s="7"/>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="5"/>
       <c r="B20" t="s">
         <v>3</v>
       </c>
       <c r="C20" s="7"/>
       <c r="D20" s="6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E20" s="6"/>
       <c r="F20" s="6"/>
@@ -878,14 +863,14 @@
       <c r="H20" s="6"/>
       <c r="I20" s="7"/>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="5"/>
       <c r="B21" t="s">
         <v>3</v>
       </c>
       <c r="C21" s="7"/>
       <c r="D21" s="6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
@@ -893,14 +878,14 @@
       <c r="H21" s="6"/>
       <c r="I21" s="7"/>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="5"/>
       <c r="B22" t="s">
         <v>3</v>
       </c>
       <c r="C22" s="7"/>
       <c r="D22" s="6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E22" s="6"/>
       <c r="F22" s="6"/>
@@ -908,14 +893,14 @@
       <c r="H22" s="6"/>
       <c r="I22" s="7"/>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="5"/>
       <c r="B23" t="s">
         <v>3</v>
       </c>
       <c r="C23" s="7"/>
       <c r="D23" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E23" s="6"/>
       <c r="F23" s="6"/>
@@ -923,14 +908,14 @@
       <c r="H23" s="6"/>
       <c r="I23" s="7"/>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="5"/>
       <c r="B24" t="s">
         <v>3</v>
       </c>
       <c r="C24" s="7"/>
       <c r="D24" s="6" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E24" s="6"/>
       <c r="F24" s="6"/>
@@ -938,14 +923,14 @@
       <c r="H24" s="6"/>
       <c r="I24" s="7"/>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="5"/>
       <c r="B25" t="s">
         <v>3</v>
       </c>
       <c r="C25" s="7"/>
       <c r="D25" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E25" s="6"/>
       <c r="F25" s="6"/>
@@ -953,14 +938,14 @@
       <c r="H25" s="6"/>
       <c r="I25" s="7"/>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="5"/>
       <c r="B26" t="s">
         <v>3</v>
       </c>
       <c r="C26" s="7"/>
       <c r="D26" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26" s="6"/>
       <c r="F26" s="6"/>
@@ -968,7 +953,7 @@
       <c r="H26" s="6"/>
       <c r="I26" s="7"/>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="5"/>
       <c r="C27" s="7"/>
       <c r="D27" s="6"/>
@@ -978,29 +963,24 @@
       <c r="H27" s="6"/>
       <c r="I27" s="7"/>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="5"/>
-      <c r="B28" t="s">
-        <v>4</v>
-      </c>
       <c r="C28" s="7"/>
-      <c r="D28" s="6" t="s">
-        <v>30</v>
-      </c>
+      <c r="D28" s="6"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="7"/>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="5"/>
       <c r="B29" t="s">
         <v>4</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E29" s="6"/>
       <c r="F29" s="6"/>
@@ -1008,14 +988,14 @@
       <c r="H29" s="6"/>
       <c r="I29" s="7"/>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="5"/>
       <c r="B30" t="s">
         <v>4</v>
       </c>
       <c r="C30" s="7"/>
       <c r="D30" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E30" s="6"/>
       <c r="F30" s="6"/>
@@ -1023,14 +1003,14 @@
       <c r="H30" s="6"/>
       <c r="I30" s="7"/>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="5"/>
       <c r="B31" t="s">
         <v>4</v>
       </c>
       <c r="C31" s="7"/>
       <c r="D31" s="6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E31" s="6"/>
       <c r="F31" s="6"/>
@@ -1038,24 +1018,29 @@
       <c r="H31" s="6"/>
       <c r="I31" s="7"/>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="5"/>
+      <c r="B32" t="s">
+        <v>4</v>
+      </c>
       <c r="C32" s="7"/>
-      <c r="D32" s="6"/>
+      <c r="D32" s="6" t="s">
+        <v>32</v>
+      </c>
       <c r="E32" s="6"/>
       <c r="F32" s="6"/>
       <c r="G32" s="6"/>
       <c r="H32" s="6"/>
       <c r="I32" s="7"/>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="5"/>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C33" s="7"/>
       <c r="D33" s="6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E33" s="6"/>
       <c r="F33" s="6"/>
@@ -1063,14 +1048,14 @@
       <c r="H33" s="6"/>
       <c r="I33" s="7"/>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="5"/>
       <c r="B34" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E34" s="6"/>
       <c r="F34" s="6"/>
@@ -1078,14 +1063,14 @@
       <c r="H34" s="6"/>
       <c r="I34" s="7"/>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="5"/>
       <c r="B35" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C35" s="7"/>
       <c r="D35" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E35" s="6"/>
       <c r="F35" s="6"/>
@@ -1093,29 +1078,24 @@
       <c r="H35" s="6"/>
       <c r="I35" s="7"/>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="5"/>
-      <c r="B36" t="s">
-        <v>5</v>
-      </c>
       <c r="C36" s="7"/>
-      <c r="D36" s="6" t="s">
-        <v>37</v>
-      </c>
+      <c r="D36" s="6"/>
       <c r="E36" s="6"/>
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
       <c r="I36" s="7"/>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="5"/>
       <c r="B37" t="s">
         <v>5</v>
       </c>
       <c r="C37" s="7"/>
       <c r="D37" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E37" s="6"/>
       <c r="F37" s="6"/>
@@ -1123,14 +1103,14 @@
       <c r="H37" s="6"/>
       <c r="I37" s="7"/>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="5"/>
       <c r="B38" t="s">
         <v>5</v>
       </c>
       <c r="C38" s="7"/>
       <c r="D38" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E38" s="6"/>
       <c r="F38" s="6"/>
@@ -1138,14 +1118,14 @@
       <c r="H38" s="6"/>
       <c r="I38" s="7"/>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="5"/>
       <c r="B39" t="s">
         <v>5</v>
       </c>
       <c r="C39" s="7"/>
       <c r="D39" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E39" s="6"/>
       <c r="F39" s="6"/>
@@ -1153,24 +1133,29 @@
       <c r="H39" s="6"/>
       <c r="I39" s="7"/>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="5"/>
+      <c r="B40" t="s">
+        <v>5</v>
+      </c>
       <c r="C40" s="7"/>
-      <c r="D40" s="6"/>
+      <c r="D40" s="6" t="s">
+        <v>39</v>
+      </c>
       <c r="E40" s="6"/>
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
       <c r="I40" s="7"/>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="5"/>
       <c r="B41" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C41" s="7"/>
       <c r="D41" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E41" s="6"/>
       <c r="F41" s="6"/>
@@ -1178,14 +1163,14 @@
       <c r="H41" s="6"/>
       <c r="I41" s="7"/>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="5"/>
       <c r="B42" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C42" s="7"/>
       <c r="D42" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E42" s="6"/>
       <c r="F42" s="6"/>
@@ -1193,14 +1178,14 @@
       <c r="H42" s="6"/>
       <c r="I42" s="7"/>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="5"/>
       <c r="B43" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C43" s="7"/>
       <c r="D43" s="6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E43" s="6"/>
       <c r="F43" s="6"/>
@@ -1208,14 +1193,14 @@
       <c r="H43" s="6"/>
       <c r="I43" s="7"/>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="5"/>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C44" s="7"/>
       <c r="D44" s="6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E44" s="6"/>
       <c r="F44" s="6"/>
@@ -1223,14 +1208,14 @@
       <c r="H44" s="6"/>
       <c r="I44" s="7"/>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="5"/>
       <c r="B45" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C45" s="7"/>
       <c r="D45" s="6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E45" s="6"/>
       <c r="F45" s="6"/>
@@ -1238,14 +1223,14 @@
       <c r="H45" s="6"/>
       <c r="I45" s="7"/>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="5"/>
       <c r="B46" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C46" s="7"/>
       <c r="D46" s="6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E46" s="6"/>
       <c r="F46" s="6"/>
@@ -1253,14 +1238,14 @@
       <c r="H46" s="6"/>
       <c r="I46" s="7"/>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="5"/>
       <c r="B47" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C47" s="7"/>
       <c r="D47" s="6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E47" s="6"/>
       <c r="F47" s="6"/>
@@ -1268,68 +1253,8 @@
       <c r="H47" s="6"/>
       <c r="I47" s="7"/>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A48" s="5"/>
-      <c r="B48" t="s">
-        <v>6</v>
-      </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="E48" s="6"/>
-      <c r="F48" s="6"/>
-      <c r="G48" s="6"/>
-      <c r="H48" s="6"/>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="I48" s="7"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A49" s="5"/>
-      <c r="B49" t="s">
-        <v>6</v>
-      </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="E49" s="6"/>
-      <c r="F49" s="6"/>
-      <c r="G49" s="6"/>
-      <c r="H49" s="6"/>
-      <c r="I49" s="7"/>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A50" s="5"/>
-      <c r="B50" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
-      <c r="H50" s="6"/>
-      <c r="I50" s="7"/>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A51" s="5"/>
-      <c r="B51" t="s">
-        <v>6</v>
-      </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="E51" s="6"/>
-      <c r="F51" s="6"/>
-      <c r="G51" s="6"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="7"/>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="I52" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
